--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -592,9 +592,7 @@
       <c r="G5" s="1" t="n">
         <v>101.19</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1031,4 +1032,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>711.4400000000001</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>704.95</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>712.26</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>700.91</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>34822164</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>62106.66</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-1669.7</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-2.62</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>63764.88</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>63814.89</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>61561.13</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>297</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.28</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.95</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.85273</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.00154</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.85426</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.8555199999999999</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.85198</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>431252</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5603</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5602</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5616</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5581</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>728443</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.41733</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.00276</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.42015</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.42086</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.41552</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>356115</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98226</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00171</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.9839599999999999</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98592</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.97848</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>318311</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>58.292</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-1.692</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-2.82</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>59.984</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>61.023</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>57.248</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>193529</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4077.58</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>-28.6</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4106.19</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4133.73</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4022.47</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>206714</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5704</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.0011</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5693</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5714</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5687</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>248875</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.61807</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00249</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.62057</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.62067</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.61465</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>432384</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>162.63</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>162.106</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>162.707</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>162.041</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>333693</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92299</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00046</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.9225</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.92376</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92113</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>362230</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.80849</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>9.000000000000001e-05</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.80841</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.81081</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.8063900000000001</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>358931</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>07/08/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -1213,9 +1213,7 @@
       <c r="G5" s="1" t="n">
         <v>100.95</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1652,4 +1653,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>717.74</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-1.95</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>723.85</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>724.36</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>710.23</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>32186877</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>16:29 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>64980.07</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>409.51</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>64585.36</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>65574.84</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>64488.46</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>321</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>100.5</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.42</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>100.89</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.03</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.8467</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>-0.0062</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>-0.73</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.8529</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.85393</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.84551</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>471480</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5642</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>-0.0002</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.5667</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5638</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>676183</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.40415</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.00194</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.14</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.40609</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.40772</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.4025</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>306518</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98372</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>0.00308</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98063</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.9847399999999999</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.9801</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>275627</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>57.78</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>-0.92</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>-1.57</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>58.7</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>59.056</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>56.633</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>176264</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4060.59</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4052.97</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4079.85</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4018.09</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>179871</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5736</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>-0.0019</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5755</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5768</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5728</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>242035</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.60962</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>0.00382</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60581</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.61072</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60475</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>392923</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>162.194</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.07099999999999999</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>162.264</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>162.419</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>161.897</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>366464</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.9232900000000001</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>-0.00087</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92415</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.926</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92214</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>388957</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.8053900000000001</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>-0.0038</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.80919</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.81146</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.8034</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>370949</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>07/15/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -1834,9 +1834,7 @@
       <c r="G5" s="1" t="n">
         <v>100.35</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>

--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -10,6 +10,7 @@
     <sheet name="Week1" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Week2" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Week3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Week4" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2273,4 +2274,626 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Latest</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Change</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>%Change</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Volume</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NQM26</t>
+        </is>
+      </c>
+      <c r="B2" s="1" t="n">
+        <v>30263.35</v>
+      </c>
+      <c r="C2" s="1" t="n">
+        <v>575.85</v>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>30290</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>29758.5</v>
+      </c>
+      <c r="H2" s="3" t="n">
+        <v>12210</v>
+      </c>
+      <c r="I2" s="4" t="inlineStr">
+        <is>
+          <t>06/18/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="B3" s="1" t="n">
+        <v>705.35</v>
+      </c>
+      <c r="C3" s="1" t="n">
+        <v>-3.62</v>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>-0.51</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>703.62</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>709.65</v>
+      </c>
+      <c r="G3" s="1" t="n">
+        <v>703.62</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>22797209</v>
+      </c>
+      <c r="I3" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="n">
+        <v>65918.2</v>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>-463.73</v>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>66358.48</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>66720.07000000001</v>
+      </c>
+      <c r="G4" s="1" t="n">
+        <v>65560</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>264</v>
+      </c>
+      <c r="I4" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>DXY</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="n">
+        <v>101.14</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>101.2</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>101.02</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>17:39 ET</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EURGBP</t>
+        </is>
+      </c>
+      <c r="B6" s="1" t="n">
+        <v>0.85325</v>
+      </c>
+      <c r="C6" s="1" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0.85216</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>0.85402</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>0.85188</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>459451</v>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AUDCHF</t>
+        </is>
+      </c>
+      <c r="B7" s="1" t="n">
+        <v>0.5698</v>
+      </c>
+      <c r="C7" s="1" t="n">
+        <v>0.0009</v>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0.5689</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>0.5675</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>592705</v>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>USDCAD</t>
+        </is>
+      </c>
+      <c r="B8" s="1" t="n">
+        <v>1.40875</v>
+      </c>
+      <c r="C8" s="1" t="n">
+        <v>-0.0021</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>1.41086</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>1.4112</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.40766</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>273180</v>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUDCAD</t>
+        </is>
+      </c>
+      <c r="B9" s="1" t="n">
+        <v>0.98568</v>
+      </c>
+      <c r="C9" s="1" t="n">
+        <v>-0.00177</v>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0.98745</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0.98882</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>0.98381</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>241865</v>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>NQZ25</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="n">
+        <v>25132.79</v>
+      </c>
+      <c r="C10" s="1" t="n">
+        <v>104.54</v>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>25002.5</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>25160</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>24977.5</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>6987</v>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>ESZ25</t>
+        </is>
+      </c>
+      <c r="B11" s="1" t="n">
+        <v>6796.54</v>
+      </c>
+      <c r="C11" s="1" t="n">
+        <v>18.29</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>6772.25</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>6802.75</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>22237</v>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>12/19/25</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>XAGUSD</t>
+        </is>
+      </c>
+      <c r="B12" s="1" t="n">
+        <v>59.71</v>
+      </c>
+      <c r="C12" s="1" t="n">
+        <v>0.919</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>58.79</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>60.907</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>58.741</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>146899</v>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="n">
+        <v>4130.13</v>
+      </c>
+      <c r="C13" s="1" t="n">
+        <v>52.28</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>4077.83</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>4165.96</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>4077.18</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>184850</v>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>CADCHF</t>
+        </is>
+      </c>
+      <c r="B14" s="1" t="n">
+        <v>0.5780999999999999</v>
+      </c>
+      <c r="C14" s="1" t="n">
+        <v>0.002</v>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="E14" s="1" t="n">
+        <v>0.5760999999999999</v>
+      </c>
+      <c r="F14" s="1" t="n">
+        <v>0.5785</v>
+      </c>
+      <c r="G14" s="1" t="n">
+        <v>0.5758</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>205632</v>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EURCAD</t>
+        </is>
+      </c>
+      <c r="B15" s="1" t="n">
+        <v>1.60765</v>
+      </c>
+      <c r="C15" s="1" t="n">
+        <v>-0.00042</v>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="E15" s="1" t="n">
+        <v>1.60808</v>
+      </c>
+      <c r="F15" s="1" t="n">
+        <v>1.60925</v>
+      </c>
+      <c r="G15" s="1" t="n">
+        <v>1.60654</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>337936</v>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>USDJPY</t>
+        </is>
+      </c>
+      <c r="B16" s="1" t="n">
+        <v>163.156</v>
+      </c>
+      <c r="C16" s="1" t="n">
+        <v>-0.032</v>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="E16" s="1" t="n">
+        <v>163.188</v>
+      </c>
+      <c r="F16" s="1" t="n">
+        <v>163.224</v>
+      </c>
+      <c r="G16" s="1" t="n">
+        <v>162.682</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>358078</v>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EURCHF</t>
+        </is>
+      </c>
+      <c r="B17" s="1" t="n">
+        <v>0.92942</v>
+      </c>
+      <c r="C17" s="1" t="n">
+        <v>0.00297</v>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="E17" s="1" t="n">
+        <v>0.92644</v>
+      </c>
+      <c r="F17" s="1" t="n">
+        <v>0.9297299999999999</v>
+      </c>
+      <c r="G17" s="1" t="n">
+        <v>0.92611</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>341026</v>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>USDCHF</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="n">
+        <v>0.81442</v>
+      </c>
+      <c r="C18" s="1" t="n">
+        <v>0.00164</v>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>0.81279</v>
+      </c>
+      <c r="F18" s="1" t="n">
+        <v>0.81482</v>
+      </c>
+      <c r="G18" s="1" t="n">
+        <v>0.81138</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>336735</v>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>07/22/26</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/outputs/july.xlsx
+++ b/outputs/july.xlsx
@@ -2455,9 +2455,7 @@
       <c r="G5" s="1" t="n">
         <v>101.02</v>
       </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
+      <c r="H5" s="3" t="n"/>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>17:39 ET</t>
